--- a/artfynd/A 23403-2026 artfynd.xlsx
+++ b/artfynd/A 23403-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95482477</v>
+        <v>95482481</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539440.8887523751</v>
+        <v>539313</v>
       </c>
       <c r="R2" t="n">
-        <v>7245262.937306471</v>
+        <v>7245247</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95482481</v>
+        <v>95482477</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539313.4655734703</v>
+        <v>539441</v>
       </c>
       <c r="R3" t="n">
-        <v>7245247.435575497</v>
+        <v>7245263</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,118 +866,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>95482480</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>539299.0669992806</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7245260.199964107</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
